--- a/assessment_forms/039_geotechnical_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/039_geotechnical_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>user_input</t>
+          <t>geotechnical_education</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>What is your educational background in geotechnical fields?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>geotechnical_education</t>
+          <t>geotechnical_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>geotechnical_education</t>
+          <t>How many years of experience do you have in geotechnical fields?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>geotechnical_experience</t>
+          <t>geotechnical_skills</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>geotechnical_experience</t>
+          <t>Which geotechnical skills do you possess (select all that apply)?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>geotechnical_skills</t>
+          <t>geotechnical_certifications</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>geotechnical_skills</t>
+          <t>What are your geotechnical certifications?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>geotechnical_certifications</t>
+          <t>geotechnical_location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>geotechnical_certifications</t>
+          <t>Where is your geotechnical location of interest (select one)?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,63 +630,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>user_comments</t>
+          <t>geotechnical_references</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>user_comments</t>
+          <t>What references can you provide for your geotechnical knowledge (select all that apply)?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>geotechnical_other</t>
+          <t>geotechnical_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>geotechnical_other</t>
+          <t>What is your geotechnical time zone (select one)?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>geotechnical_time</t>
+          <t>geotechnical_other_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>geotechnical_time</t>
+          <t>What other geotechnical information do you want to provide?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,63 +699,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>geotechnical_location</t>
+          <t>geotechnical_other_comments</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>geotechnical_location</t>
+          <t>What other geotechnical comments do you have?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>geotechnical_references</t>
+          <t>geotechnical_other_time</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>geotechnical_references</t>
+          <t>What is your geotechnical time (select one)?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>geotechnical_other_info</t>
+          <t>geotechnical_other_location</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>geotechnical_other_info</t>
+          <t>What is your geotechnical location (select one)?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>geotechnical_other_comments</t>
+          <t>geotechnical_other_references</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>geotechnical_other_comments</t>
+          <t>What other geotechnical references do you want to provide (select all that apply)?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,40 +791,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>geotechnical_signature</t>
+          <t>geotechnical_other_comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>geotechnical_signature</t>
+          <t>Geotechnical Other Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>geotechnical_other</t>
+          <t>geotechnical_other_signature</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>geotechnical_other</t>
+          <t>Can you provide a geotechnical signature?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>geotechnical_other_info</t>
+          <t>geotechnical_other_other_info</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>geotechnical_other_info</t>
+          <t>Geotechnical Other Other Info</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>geotechnical_other_comments</t>
+          <t>geotechnical_other_other_comments</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>geotechnical_other_comments</t>
+          <t>Geotechnical Other Other Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>geotechnical_other_time</t>
+          <t>geotechnical_other_other_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>geotechnical_other_time</t>
+          <t>Geotechnical Other Other Time</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>geotechnical_other_location</t>
+          <t>geotechnical_other_other_location</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>geotechnical_other_location</t>
+          <t>Geotechnical Other Other Location</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>geotechnical_other_references</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>geotechnical_other_references</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_time</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_location</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_location</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_references</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_references</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>geotechnical_other_other_comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>geotechnical_bachelor's_degree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Geotechnical Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>geotechnical_master's_degree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Geotechnical Master's Degree</t>
         </is>
       </c>
     </row>
@@ -1165,352 +1004,607 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>geotechnical_ph.d.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Geotechnical Ph.D.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>geotechnical_experience_choices</t>
+          <t>geotechnical_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>rock_mechanics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Rock mechanics</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>geotechnical_experience_choices</t>
+          <t>geotechnical_skills_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>soil_mechanics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Soil mechanics</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>geotechnical_certifications_choices</t>
+          <t>geotechnical_skills_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>structural_analysis</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Structural analysis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>geotechnical_certifications_choices</t>
+          <t>geotechnical_skills_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>geotechnical_engineering_design</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Geotechnical engineering design</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>geotechnical_location_choices</t>
+          <t>geotechnical_skills_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>geotechnical_site_investigation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Geotechnical site investigation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>geotechnical_location_choices</t>
+          <t>geotechnical_certifications_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>geotechnical_certification_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Geotechnical certification 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>geotechnical_references_choices</t>
+          <t>geotechnical_certifications_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>geotechnical_certification_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Geotechnical certification 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>geotechnical_references_choices</t>
+          <t>geotechnical_certifications_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>geotechnical_certification_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Geotechnical certification 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>geotechnical_signature_choices</t>
+          <t>geotechnical_location_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>geotechnical_signature_choices</t>
+          <t>geotechnical_location_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>geotechnical_other_choices</t>
+          <t>geotechnical_location_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>geotechnical_other_choices</t>
+          <t>geotechnical_references_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>reference_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Reference 1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>geotechnical_other_location_choices</t>
+          <t>geotechnical_references_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>reference_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Reference 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>geotechnical_other_location_choices</t>
+          <t>geotechnical_references_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>reference_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Reference 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>geotechnical_other_references_choices</t>
+          <t>geotechnical_time_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>geotechnical_other_references_choices</t>
+          <t>geotechnical_time_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>geotechnical_other_other_location_choices</t>
+          <t>geotechnical_time_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>geotechnical_other_other_location_choices</t>
+          <t>geotechnical_other_time_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>geotechnical_other_other_references_choices</t>
+          <t>geotechnical_other_time_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>geotechnical_other_other_references_choices</t>
+          <t>geotechnical_other_time_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>geotechnical_other_location_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>geotechnical_other_location_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>geotechnical_other_location_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>geotechnical_other_references_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>reference_1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Reference 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>geotechnical_other_references_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>reference_2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Reference 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>geotechnical_other_references_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>reference_3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Reference 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>geotechnical_other_signature_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>geotechnical_other_signature_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>geotechnical_other_signature_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>geotechnical_other_other_time_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>geotechnical_other_other_time_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>geotechnical_other_other_time_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>geotechnical_other_other_location_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>geotechnical_other_other_location_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>geotechnical_other_other_location_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
